--- a/data/trans_dic/P20-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P20-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 8,15</t>
+          <t>5,12; 8,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,37; 12,45</t>
+          <t>8,51; 12,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 9,36</t>
+          <t>5,58; 9,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,62; 13,19</t>
+          <t>8,29; 13,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,26</t>
+          <t>6,29; 9,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,89</t>
+          <t>8,5; 11,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,41</t>
+          <t>6,46; 10,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,98</t>
+          <t>6,16; 8,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,32</t>
+          <t>6,11; 8,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 11,48</t>
+          <t>8,92; 11,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 9,25</t>
+          <t>6,57; 9,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,99</t>
+          <t>7,6; 10,14</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,54</t>
+          <t>2,0; 3,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,88</t>
+          <t>3,8; 5,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 4,89</t>
+          <t>3,16; 4,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,21</t>
+          <t>2,85; 5,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,74</t>
+          <t>5,96; 8,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,82; 10,51</t>
+          <t>7,8; 10,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,54</t>
+          <t>6,05; 8,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,44</t>
+          <t>3,82; 6,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,69</t>
+          <t>4,13; 5,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 7,7</t>
+          <t>6,03; 7,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 6,35</t>
+          <t>4,82; 6,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,5</t>
+          <t>3,79; 5,49</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,27</t>
+          <t>2,69; 6,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,81</t>
+          <t>1,53; 5,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,36</t>
+          <t>2,92; 7,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 8,08</t>
+          <t>4,16; 8,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,88</t>
+          <t>5,03; 10,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 12,64</t>
+          <t>7,12; 12,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 11,42</t>
+          <t>6,46; 11,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,48</t>
+          <t>5,0; 8,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,19</t>
+          <t>4,27; 7,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,77</t>
+          <t>4,68; 7,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,35</t>
+          <t>5,2; 8,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 7,61</t>
+          <t>5,09; 7,68</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,92</t>
+          <t>3,49; 4,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 7,09</t>
+          <t>5,25; 6,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 5,74</t>
+          <t>4,11; 5,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,35</t>
+          <t>4,15; 6,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,44</t>
+          <t>6,55; 8,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 10,61</t>
+          <t>8,5; 10,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 8,69</t>
+          <t>6,9; 8,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 6,85</t>
+          <t>4,72; 6,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,34</t>
+          <t>5,23; 6,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 8,48</t>
+          <t>7,22; 8,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 6,98</t>
+          <t>5,74; 6,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 6,34</t>
+          <t>4,85; 6,35</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>53362; 84049</t>
+          <t>52788; 84433</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>81533; 121363</t>
+          <t>82942; 122288</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42403; 70576</t>
+          <t>42070; 70371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44380; 67905</t>
+          <t>42697; 68179</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82422; 121819</t>
+          <t>82681; 120165</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>114126; 159048</t>
+          <t>113653; 159473</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64176; 103576</t>
+          <t>64301; 100311</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46882; 67602</t>
+          <t>46395; 67322</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>144853; 195241</t>
+          <t>143288; 193527</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>203501; 265407</t>
+          <t>206367; 267648</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>114223; 161749</t>
+          <t>114854; 161891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94535; 126715</t>
+          <t>96331; 128588</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32555; 60012</t>
+          <t>33797; 62547</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75541; 115445</t>
+          <t>74583; 110905</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66137; 101546</t>
+          <t>65611; 102998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65249; 119330</t>
+          <t>65325; 118302</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>95111; 138689</t>
+          <t>94558; 134492</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>137442; 184785</t>
+          <t>137118; 187544</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>122201; 169763</t>
+          <t>120324; 166487</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86604; 144182</t>
+          <t>85464; 144380</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>136822; 186751</t>
+          <t>135391; 186121</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>223392; 286552</t>
+          <t>224459; 287613</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>198694; 258066</t>
+          <t>195720; 258278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>166997; 249218</t>
+          <t>171426; 248397</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14861; 34507</t>
+          <t>14831; 34843</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6973; 23164</t>
+          <t>7348; 25631</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16513; 40243</t>
+          <t>15952; 38976</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26273; 52215</t>
+          <t>26914; 53104</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25145; 47085</t>
+          <t>23965; 48576</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32350; 57972</t>
+          <t>32655; 57953</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35124; 62697</t>
+          <t>35474; 60442</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33503; 56000</t>
+          <t>32995; 56830</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44491; 73870</t>
+          <t>43842; 75411</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43158; 73010</t>
+          <t>43969; 74832</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57887; 91514</t>
+          <t>56940; 92411</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65049; 99413</t>
+          <t>66559; 100377</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>114463; 161027</t>
+          <t>114249; 160390</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>179262; 242348</t>
+          <t>179413; 236086</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>140185; 193800</t>
+          <t>138698; 193764</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>144881; 219301</t>
+          <t>143214; 218900</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>221883; 285315</t>
+          <t>221283; 281499</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>304630; 377065</t>
+          <t>301982; 375510</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>242627; 307018</t>
+          <t>243585; 306559</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>174680; 249946</t>
+          <t>172395; 247093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>350217; 422044</t>
+          <t>347926; 424115</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>499610; 591127</t>
+          <t>503199; 600991</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>395920; 482044</t>
+          <t>396379; 479854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>343633; 450233</t>
+          <t>344450; 451417</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P20-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,18</t>
+          <t>5,18; 8,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,51; 12,55</t>
+          <t>8,32; 12,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,33</t>
+          <t>5,57; 9,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 13,24</t>
+          <t>8,0; 12,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 9,14</t>
+          <t>6,24; 9,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 11,92</t>
+          <t>8,59; 11,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,08</t>
+          <t>6,39; 10,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,94</t>
+          <t>6,14; 8,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 8,25</t>
+          <t>6,2; 8,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,92; 11,57</t>
+          <t>8,9; 11,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 9,26</t>
+          <t>6,7; 9,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,14</t>
+          <t>7,35; 9,74</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,69</t>
+          <t>1,99; 3,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,65</t>
+          <t>3,84; 5,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,96</t>
+          <t>3,18; 4,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,17</t>
+          <t>3,84; 5,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 8,47</t>
+          <t>6,02; 8,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 10,67</t>
+          <t>7,76; 10,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,37</t>
+          <t>6,2; 8,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,45</t>
+          <t>5,25; 7,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 5,67</t>
+          <t>4,13; 5,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 7,73</t>
+          <t>6,09; 7,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,35</t>
+          <t>4,84; 6,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,49</t>
+          <t>4,84; 6,19</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>6,78%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>6,7%</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,33</t>
+          <t>2,63; 6,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,33</t>
+          <t>1,44; 4,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,21</t>
+          <t>4,0; 8,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 10,2</t>
+          <t>5,16; 9,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 12,64</t>
+          <t>6,87; 12,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 11,01</t>
+          <t>6,58; 11,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,6</t>
+          <t>5,27; 8,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,34</t>
+          <t>4,39; 7,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,96</t>
+          <t>4,49; 7,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,43</t>
+          <t>5,21; 8,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,68</t>
+          <t>5,02; 7,64</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,9</t>
+          <t>3,48; 4,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 6,91</t>
+          <t>5,28; 6,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,74</t>
+          <t>4,14; 5,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,34</t>
+          <t>5,09; 6,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,33</t>
+          <t>6,44; 8,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 10,57</t>
+          <t>8,59; 10,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 8,68</t>
+          <t>6,82; 8,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,77</t>
+          <t>5,89; 7,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,37</t>
+          <t>5,19; 6,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 8,62</t>
+          <t>7,17; 8,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 6,94</t>
+          <t>5,7; 6,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,35</t>
+          <t>5,62; 6,79</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55601</t>
+          <t>58237</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55959</t>
+          <t>60498</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>111561</t>
+          <t>118735</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52788; 84433</t>
+          <t>53493; 84166</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>82942; 122288</t>
+          <t>81098; 121410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42070; 70371</t>
+          <t>42037; 71148</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42697; 68179</t>
+          <t>46290; 72805</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82681; 120165</t>
+          <t>82028; 121992</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>113653; 159473</t>
+          <t>114938; 158396</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64301; 100311</t>
+          <t>63535; 101138</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46395; 67322</t>
+          <t>50405; 73175</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>143288; 193527</t>
+          <t>145535; 193679</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>206367; 267648</t>
+          <t>205834; 264935</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>114854; 161891</t>
+          <t>117097; 163888</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96331; 128588</t>
+          <t>102932; 136292</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94766</t>
+          <t>105588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>116455</t>
+          <t>134615</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>240203</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33797; 62547</t>
+          <t>33659; 59581</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74583; 110905</t>
+          <t>75289; 114873</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65611; 102998</t>
+          <t>66053; 103168</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65325; 118302</t>
+          <t>85696; 127624</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94558; 134492</t>
+          <t>95645; 138588</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>137118; 187544</t>
+          <t>136328; 185887</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120324; 166487</t>
+          <t>123300; 169427</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85464; 144380</t>
+          <t>113965; 158435</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>135391; 186121</t>
+          <t>135627; 185518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>224459; 287613</t>
+          <t>226432; 288195</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>195720; 258278</t>
+          <t>196704; 256306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>171426; 248397</t>
+          <t>212855; 272397</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36988</t>
+          <t>40486</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44263</t>
+          <t>49799</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81251</t>
+          <t>90285</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14831; 34843</t>
+          <t>14471; 34967</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7348; 25631</t>
+          <t>6906; 23901</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15952; 38976</t>
+          <t>15964; 38989</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26914; 53104</t>
+          <t>28484; 57381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23965; 48576</t>
+          <t>24583; 47081</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32655; 57953</t>
+          <t>31503; 57688</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35474; 60442</t>
+          <t>36127; 62773</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32995; 56830</t>
+          <t>38760; 63427</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>43842; 75411</t>
+          <t>45029; 73531</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43969; 74832</t>
+          <t>42236; 72657</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56940; 92411</t>
+          <t>57134; 93242</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66559; 100377</t>
+          <t>72575; 110520</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>187356</t>
+          <t>204311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>216677</t>
+          <t>244913</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>404033</t>
+          <t>449223</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>114249; 160390</t>
+          <t>113852; 161439</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>179413; 236086</t>
+          <t>180594; 238467</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>138698; 193764</t>
+          <t>139987; 190747</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>143214; 218900</t>
+          <t>179313; 237195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>221283; 281499</t>
+          <t>217521; 281291</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>301982; 375510</t>
+          <t>305132; 373849</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>243585; 306559</t>
+          <t>240987; 308599</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>172395; 247093</t>
+          <t>219441; 273479</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>347926; 424115</t>
+          <t>345434; 423699</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>503199; 600991</t>
+          <t>500036; 599415</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>396379; 479854</t>
+          <t>393810; 480091</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>344450; 451417</t>
+          <t>407373; 492291</t>
         </is>
       </c>
     </row>
